--- a/draft/database_eft.xlsx
+++ b/draft/database_eft.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="182">
-  <si>
-    <t>quest</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="235">
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>таблица со всеми квестами</t>
@@ -439,12 +439,12 @@
     <t>up_level</t>
   </si>
   <si>
-    <t>TODO... таблица бартера</t>
-  </si>
-  <si>
     <t>kill_zryachy</t>
   </si>
   <si>
+    <t>min_fence_loyalty</t>
+  </si>
+  <si>
     <t>map</t>
   </si>
   <si>
@@ -469,12 +469,21 @@
     <t>таблица ценами продажи торговцев</t>
   </si>
   <si>
+    <t>items_barter</t>
+  </si>
+  <si>
+    <t>таблица с бартером</t>
+  </si>
+  <si>
     <t>image</t>
   </si>
   <si>
     <t>max_pmc</t>
   </si>
   <si>
+    <t>unlock_flea_market</t>
+  </si>
+  <si>
     <t>trader</t>
   </si>
   <si>
@@ -484,6 +493,9 @@
     <t>valuta</t>
   </si>
   <si>
+    <t>max_count</t>
+  </si>
+  <si>
     <t>Название карты</t>
   </si>
   <si>
@@ -502,6 +514,9 @@
     <t>тип предмета</t>
   </si>
   <si>
+    <t>с какого уровня доступен на барахолке</t>
+  </si>
+  <si>
     <t>ID предложения</t>
   </si>
   <si>
@@ -517,6 +532,12 @@
     <t>цена продажи</t>
   </si>
   <si>
+    <t>сколько можно купить за 1 завоз</t>
+  </si>
+  <si>
+    <t>количество</t>
+  </si>
+  <si>
     <t>Избыточно будет если сделать ID как уникальный ключ</t>
   </si>
   <si>
@@ -529,6 +550,9 @@
     <t>у каждой категории предметов есть свои категории свойств (как у бутылки воды может быть 1.42 MOA?)</t>
   </si>
   <si>
+    <t>вот чем и грешат старые справочники. До релиза было просто: барахолка доступна только с уровня N, и она давала доступ абсолютно ко всем предметам. Теперь же мало того, что не каждый предмет доступен на барахолке, так еще и становится доступен с уровня N. Можно было привязать доступность к категории предмета, но некоторые предметы -- исключение из правил. Например, ключи можно покупать только с 25 уровня, но ключи от "меченок" доступны с 35 уровня, а танковый аккум хоть и относится к категории электроника (доступен с 20 уровня), но доступен с 40 уровня. Если поле на записи здесь пустое, значит предмет не доступен на барахолке, потому что сама барахолка открывается с 15 уровня</t>
+  </si>
+  <si>
     <t>поскольку один и тот же предмет могут купить разные торговцы за разную стоимость, поэтому идея "1 item = 1 item_purchase" не подходит. Если цены нет, значит торговец не покупает</t>
   </si>
   <si>
@@ -541,10 +565,7 @@
     <t>да, пока тогровцы скупают за рубль, кроме миротворца, однако судя по развитию игры, а также по наличию других валют, лучше сделать этот пункт</t>
   </si>
   <si>
-    <t>аналогично с itmes_purchase</t>
-  </si>
-  <si>
-    <t>тот, кто продает этот предмет</t>
+    <t>тот, кто продает этот предмет. Указываем по уровню лояльности</t>
   </si>
   <si>
     <t>то, за сколько продает торговец</t>
@@ -553,17 +574,155 @@
     <t>здесь проще, чем в items_purchase, потому что торговцы часто продают по разнообразной валюте</t>
   </si>
   <si>
+    <t>можно было бы привязать ID предложения к ID item, но торговец имеет наглость просить за 1 предмет несколько разных предметов</t>
+  </si>
+  <si>
+    <t>кто предлагает. Указываем по уровню лояльности</t>
+  </si>
+  <si>
+    <t>торговец может требовать за 1 предмет несколько разных, но правильней говорить несколько категорий предметов. Например, Миротворец 2LL требует за защищенный кейс Бета 1 танковый аккум, 5 военных кабелей, 3 виртекса и 3 иридиума</t>
+  </si>
+  <si>
     <t>text not null primary key</t>
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>TODO... описать каждую категорию</t>
+  </si>
+  <si>
+    <t>TODO... создать сущность, описывающая свойства из этой категории</t>
+  </si>
+  <si>
+    <t>bladed_weapons</t>
+  </si>
+  <si>
+    <t>weapons</t>
+  </si>
+  <si>
+    <t>bullets</t>
+  </si>
+  <si>
+    <t>mods</t>
+  </si>
+  <si>
+    <t>specs</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>containers</t>
+  </si>
+  <si>
+    <t>keys</t>
+  </si>
+  <si>
+    <t>armors</t>
+  </si>
+  <si>
+    <t>таблица с торговцами</t>
+  </si>
+  <si>
+    <t>trader_loyalty</t>
+  </si>
+  <si>
+    <t>таблица хранящая информацию о лояльности торговцев</t>
+  </si>
+  <si>
+    <t>items_unlocking_purchase</t>
+  </si>
+  <si>
+    <t>таблица с доступными предметами к покупке после квеста</t>
+  </si>
+  <si>
+    <t>in_raid</t>
+  </si>
+  <si>
+    <t>trader_name</t>
+  </si>
+  <si>
+    <t>loyalty_level</t>
+  </si>
+  <si>
+    <t>min_loyalty</t>
+  </si>
+  <si>
+    <t>min_turnover_amount</t>
+  </si>
+  <si>
+    <t>unlocked_in_quest</t>
+  </si>
+  <si>
+    <t>имя торговца</t>
+  </si>
+  <si>
+    <t>иконка торговца</t>
+  </si>
+  <si>
+    <t>встретить только в рейде</t>
+  </si>
+  <si>
+    <t>уровень лояльности</t>
+  </si>
+  <si>
+    <t>с каким торговцем связан LL</t>
+  </si>
+  <si>
+    <t>минимальный уровень</t>
+  </si>
+  <si>
+    <t>минимальная лояльность</t>
+  </si>
+  <si>
+    <t>минимальный оборот средств</t>
+  </si>
+  <si>
+    <t>нужно ли открывать по квесту</t>
+  </si>
+  <si>
+    <t>с каким квестом связан</t>
+  </si>
+  <si>
+    <t>торговцев немного, поэтому их имена можно использовать в качестве PK</t>
+  </si>
+  <si>
+    <t>да, смотрителя и водителя БТР сложно назвать торговцами, но они выдают квесты, а также на будущее будет запас, вдруг они не только будут выдавать квесты и оказывать услуги</t>
+  </si>
+  <si>
+    <t>опишем как id, чтобы удобнее было условия разблокировки. Благо условия разблокировки простые, нужно открыть за выполнение квестов, а повышать по простой схеме: min_level AND min_loyalty AND min_turnover_amount</t>
+  </si>
+  <si>
+    <t>проблема в том, что есть 3 типа торговцев: классическая LL (1..3 и prime), упрощенная (у скупщика, 1 и prime) и вообще без репутации (ни на что не влияет, записей о них здесь делать не нужно)</t>
+  </si>
+  <si>
+    <t>тут просто, уровней 1..3 и prime, для простоты назовем prime LL просто 4</t>
+  </si>
+  <si>
+    <t>если уровень не нужен, то просто 0</t>
+  </si>
+  <si>
+    <t>если не нужен, то просто 0</t>
+  </si>
+  <si>
+    <t>да, не все торговцы доступны сразу по 1LL, некоторых нужно открывать по сюжетному квесту "Тур", либо выполняя какой-то побочный квест (Легкие деньги часть 1 на Рефа LL1, Поручение на Егеря LL1 и Новое знакомство на Смотрителя)</t>
+  </si>
+  <si>
+    <t>берем с таблицы лояльности</t>
+  </si>
+  <si>
+    <t>какой квест разблокировывает бартер</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -594,6 +753,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -758,7 +923,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -801,6 +966,7 @@
     <xf borderId="9" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="10" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -834,18 +1000,27 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -858,8 +1033,12 @@
     <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -867,13 +1046,18 @@
     <xf borderId="10" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1095,26 +1279,29 @@
     <col customWidth="1" min="2" max="2" width="32.5"/>
     <col customWidth="1" min="3" max="3" width="30.0"/>
     <col customWidth="1" min="4" max="4" width="19.38"/>
-    <col customWidth="1" min="5" max="6" width="20.13"/>
+    <col customWidth="1" min="5" max="5" width="32.25"/>
+    <col customWidth="1" min="6" max="6" width="29.0"/>
     <col customWidth="1" min="7" max="7" width="20.63"/>
     <col customWidth="1" min="8" max="8" width="31.5"/>
-    <col customWidth="1" min="9" max="9" width="20.25"/>
-    <col customWidth="1" min="10" max="10" width="27.63"/>
-    <col customWidth="1" min="11" max="11" width="19.13"/>
+    <col customWidth="1" min="9" max="9" width="22.88"/>
+    <col customWidth="1" min="10" max="10" width="62.88"/>
+    <col customWidth="1" min="11" max="11" width="34.5"/>
     <col customWidth="1" min="12" max="12" width="24.25"/>
     <col customWidth="1" min="13" max="13" width="21.88"/>
     <col customWidth="1" min="14" max="14" width="19.75"/>
     <col customWidth="1" min="15" max="15" width="25.25"/>
     <col customWidth="1" min="16" max="16" width="20.13"/>
-    <col customWidth="1" min="17" max="17" width="21.88"/>
+    <col customWidth="1" min="17" max="17" width="26.38"/>
     <col customWidth="1" min="18" max="18" width="22.88"/>
     <col customWidth="1" min="19" max="19" width="18.63"/>
     <col customWidth="1" min="20" max="20" width="31.88"/>
     <col customWidth="1" min="21" max="21" width="30.25"/>
-    <col customWidth="1" min="22" max="23" width="23.5"/>
-    <col customWidth="1" min="24" max="24" width="13.88"/>
+    <col customWidth="1" min="22" max="22" width="23.5"/>
+    <col customWidth="1" min="23" max="23" width="28.25"/>
+    <col customWidth="1" min="24" max="24" width="26.38"/>
     <col customWidth="1" min="25" max="25" width="18.88"/>
-    <col customWidth="1" min="26" max="26" width="63.63"/>
+    <col customWidth="1" min="26" max="26" width="62.88"/>
+    <col customWidth="1" min="27" max="28" width="31.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1257,6 +1444,8 @@
       <c r="T3" s="15" t="s">
         <v>38</v>
       </c>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
@@ -1310,74 +1499,80 @@
       <c r="T4" s="15" t="s">
         <v>49</v>
       </c>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="P5" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="R5" s="18" t="s">
+      <c r="R5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="T5" s="20" t="s">
+      <c r="T5" s="21" t="s">
         <v>55</v>
       </c>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
     </row>
     <row r="6">
-      <c r="A6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="A6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="25" t="s">
         <v>58</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1387,7 +1582,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="4"/>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="26" t="s">
         <v>60</v>
       </c>
       <c r="N7" s="8" t="s">
@@ -1408,9 +1603,11 @@
       <c r="Y7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="Z7" s="27" t="s">
         <v>65</v>
       </c>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
@@ -1428,19 +1625,19 @@
       <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="30" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="7" t="s">
@@ -1479,6 +1676,8 @@
       <c r="Z8" s="9" t="s">
         <v>75</v>
       </c>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="s">
@@ -1547,6 +1746,8 @@
       <c r="Z9" s="12" t="s">
         <v>93</v>
       </c>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="31"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="s">
@@ -1615,551 +1816,938 @@
       <c r="Z10" s="12" t="s">
         <v>39</v>
       </c>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="O11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="P11" s="16" t="s">
+      <c r="P11" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="Q11" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="R11" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="T11" s="16" t="s">
+      <c r="T11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="U11" s="16" t="s">
+      <c r="U11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="V11" s="16" t="s">
+      <c r="V11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="W11" s="16" t="s">
+      <c r="W11" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="Y11" s="16" t="s">
+      <c r="Y11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="Z11" s="16" t="s">
+      <c r="Z11" s="17" t="s">
         <v>51</v>
       </c>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
     </row>
     <row r="12">
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="O12" s="30" t="s">
+      <c r="O12" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="V12" s="30" t="s">
+      <c r="V12" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="Z12" s="30" t="s">
+      <c r="Z12" s="33" t="s">
         <v>116</v>
       </c>
+      <c r="AA12" s="34"/>
+      <c r="AB12" s="34"/>
     </row>
     <row r="13">
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="J13" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="O13" s="32" t="s">
+      <c r="O13" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="V13" s="32" t="s">
+      <c r="V13" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="Z13" s="32" t="s">
+      <c r="Z13" s="36" t="s">
         <v>121</v>
       </c>
+      <c r="AA13" s="34"/>
+      <c r="AB13" s="34"/>
     </row>
     <row r="14">
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="O14" s="32" t="s">
+      <c r="O14" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="V14" s="32" t="s">
+      <c r="V14" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="Z14" s="33" t="s">
+      <c r="Z14" s="37" t="s">
         <v>120</v>
       </c>
+      <c r="AA14" s="34"/>
+      <c r="AB14" s="34"/>
     </row>
     <row r="15">
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="O15" s="32" t="s">
+      <c r="O15" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="V15" s="33" t="s">
+      <c r="V15" s="37" t="s">
         <v>129</v>
       </c>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
     </row>
     <row r="16">
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="O16" s="32" t="s">
+      <c r="O16" s="36" t="s">
         <v>132</v>
       </c>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
     </row>
     <row r="17">
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="O17" s="32" t="s">
+      <c r="O17" s="36" t="s">
         <v>135</v>
       </c>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
     </row>
     <row r="18">
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="J18" s="33" t="s">
+      <c r="J18" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="O18" s="32" t="s">
+      <c r="O18" s="36" t="s">
         <v>138</v>
       </c>
+      <c r="AA18" s="16"/>
+      <c r="AB18" s="16"/>
     </row>
     <row r="19">
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="O19" s="32" t="s">
+      <c r="O19" s="36" t="s">
         <v>139</v>
       </c>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
     </row>
     <row r="20">
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="O20" s="33" t="s">
+      <c r="O20" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="R20" s="21" t="s">
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="35" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="C21" s="34" t="s">
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="38" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="35"/>
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="E23" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
-      <c r="K23" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="Q23" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="4"/>
+      <c r="AB23" s="39"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="E24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="4"/>
+      <c r="L24" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="4"/>
+      <c r="R24" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="4"/>
+      <c r="Y24" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z24" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="4"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" s="7" t="s">
+      <c r="B25" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="H24" s="7" t="s">
+      <c r="G25" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="J25" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="M24" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q24" s="7" t="s">
+      <c r="N25" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="R25" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R24" s="7" t="s">
+      <c r="S25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="T24" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="s">
+      <c r="T25" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="U25" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="V25" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="12" t="s">
+      <c r="W25" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q25" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="R25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="T25" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>166</v>
+      <c r="Y25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="L26" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="M26" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="O26" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="R26" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="T26" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="U26" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y26" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z26" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA26" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB26" s="41" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="12" t="s">
+      <c r="G27" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="J27" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="L27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L26" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="M26" s="12" t="s">
+      <c r="M27" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="R27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="S27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="T27" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="U27" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="V27" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y27" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA27" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB27" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="O28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="R28" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="S28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="U28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="V28" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="W28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y28" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB28" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="I29" s="31"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="V29" s="33" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I30" s="31"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="V30" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="H31" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="V31" s="36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="31"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="H32" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="I32" s="31"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="V32" s="37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="45"/>
+      <c r="U33" s="45"/>
+      <c r="AA33" s="16"/>
+      <c r="AB33" s="16"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="4"/>
+      <c r="U34" s="45"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L35" s="22"/>
+      <c r="M35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O35" s="47" t="s">
+        <v>157</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="U35" s="45"/>
+      <c r="AA35" s="16"/>
+      <c r="AB35" s="16"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36" s="22"/>
+      <c r="M36" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="O36" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="P36" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q36" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="N26" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q26" s="12" t="s">
+      <c r="U36" s="45"/>
+      <c r="AA36" s="16"/>
+      <c r="AB36" s="16"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L37" s="22"/>
+      <c r="M37" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="R26" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="S26" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="37" t="s">
+      <c r="N37" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="O37" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q37" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="U37" s="45"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C38" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="H38" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L38" s="22"/>
+      <c r="M38" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" s="16" t="s">
+      <c r="N38" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N27" s="16" t="s">
+      <c r="O38" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="O27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="R27" s="16" t="s">
+      <c r="P38" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="S27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="T27" s="16" t="s">
+      <c r="Q38" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="U27" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="U28" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="U29" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="U30" s="32" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="U31" s="33" t="s">
-        <v>132</v>
-      </c>
+      <c r="U38" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="R23:U23"/>
+  <mergeCells count="16">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="M1:P1"/>
@@ -2167,6 +2755,15 @@
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="N7:R7"/>
     <mergeCell ref="U7:W7"/>
+    <mergeCell ref="F34:K34"/>
+    <mergeCell ref="N34:Q34"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="S24:W24"/>
+    <mergeCell ref="Z24:AB24"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/draft/database_eft.xlsx
+++ b/draft/database_eft.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="333">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -37,13 +37,25 @@
     <t>таблица отслеживания целей</t>
   </si>
   <si>
+    <t>trader_user_loyalty</t>
+  </si>
+  <si>
+    <t>таблица лояльности к торговцам</t>
+  </si>
+  <si>
+    <t>items_user</t>
+  </si>
+  <si>
+    <t>таблица найденых предметов</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>owner</t>
+    <t>trader</t>
   </si>
   <si>
     <t>description</t>
@@ -79,6 +91,15 @@
     <t>is_finished</t>
   </si>
   <si>
+    <t>loyalty</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>count_in_raid</t>
+  </si>
+  <si>
     <t>номер квеста</t>
   </si>
   <si>
@@ -130,10 +151,25 @@
     <t>выполнен ли?</t>
   </si>
   <si>
+    <t>торговец</t>
+  </si>
+  <si>
+    <t>лояльность к этому торговцу</t>
+  </si>
+  <si>
+    <t>предмет</t>
+  </si>
+  <si>
+    <t>количество</t>
+  </si>
+  <si>
+    <t>количество с "найдено в рейде"</t>
+  </si>
+  <si>
     <t>без комментариев</t>
   </si>
   <si>
-    <t>не требует сложной структуры, просто надо записывать правильно имя торговцев</t>
+    <t>не требует сложной структуры, от лояльности не зависит</t>
   </si>
   <si>
     <t>Тупо текст нельзя хранить, поскольку нужны скрины, возможно видео</t>
@@ -163,6 +199,12 @@
     <t>без комментариев. Также false, если null</t>
   </si>
   <si>
+    <t>да, этот столбец будет PK и FK одновременно</t>
+  </si>
+  <si>
+    <t>по умолчанию лояльность 0.00, либо +N на старте в зависимости от издания</t>
+  </si>
+  <si>
     <t>int not null primary key</t>
   </si>
   <si>
@@ -181,6 +223,15 @@
     <t>bool</t>
   </si>
   <si>
+    <t>text not null primary key FK</t>
+  </si>
+  <si>
+    <t>float not null</t>
+  </si>
+  <si>
+    <t>int not null primary key FK</t>
+  </si>
+  <si>
     <t>quest_available</t>
   </si>
   <si>
@@ -355,9 +406,6 @@
     <t>put_item</t>
   </si>
   <si>
-    <t>item</t>
-  </si>
-  <si>
     <t>competed</t>
   </si>
   <si>
@@ -484,7 +532,10 @@
     <t>unlock_flea_market</t>
   </si>
   <si>
-    <t>trader</t>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>enable_drop</t>
   </si>
   <si>
     <t>price</t>
@@ -496,6 +547,9 @@
     <t>max_count</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
     <t>Название карты</t>
   </si>
   <si>
@@ -517,12 +571,15 @@
     <t>с какого уровня доступен на барахолке</t>
   </si>
   <si>
+    <t>масса предмета</t>
+  </si>
+  <si>
+    <t>сколько можно выбросить в рейде</t>
+  </si>
+  <si>
     <t>ID предложения</t>
   </si>
   <si>
-    <t>торговец</t>
-  </si>
-  <si>
     <t>цена закупки</t>
   </si>
   <si>
@@ -535,7 +592,7 @@
     <t>сколько можно купить за 1 завоз</t>
   </si>
   <si>
-    <t>количество</t>
+    <t>номер группы</t>
   </si>
   <si>
     <t>Избыточно будет если сделать ID как уникальный ключ</t>
@@ -553,6 +610,12 @@
     <t>вот чем и грешат старые справочники. До релиза было просто: барахолка доступна только с уровня N, и она давала доступ абсолютно ко всем предметам. Теперь же мало того, что не каждый предмет доступен на барахолке, так еще и становится доступен с уровня N. Можно было привязать доступность к категории предмета, но некоторые предметы -- исключение из правил. Например, ключи можно покупать только с 25 уровня, но ключи от "меченок" доступны с 35 уровня, а танковый аккум хоть и относится к категории электроника (доступен с 20 уровня), но доступен с 40 уровня. Если поле на записи здесь пустое, значит предмет не доступен на барахолке, потому что сама барахолка открывается с 15 уровня</t>
   </si>
   <si>
+    <t>единственное, что есть у каждого предмета. Есть специфичные предметы, которые не имеют массы</t>
+  </si>
+  <si>
+    <t>если null, то в рейде выбросить нельзя</t>
+  </si>
+  <si>
     <t>поскольку один и тот же предмет могут купить разные торговцы за разную стоимость, поэтому идея "1 item = 1 item_purchase" не подходит. Если цены нет, значит торговец не покупает</t>
   </si>
   <si>
@@ -577,6 +640,9 @@
     <t>можно было бы привязать ID предложения к ID item, но торговец имеет наглость просить за 1 предмет несколько разных предметов</t>
   </si>
   <si>
+    <t>есть проблема в том, что у одного торговца есть несколько разных бартеров, поэтому идея привязывать 1 одному предмету 1 бартер -- не лучшая идея. даже если бартер уникальный, у нее все равно номер группы уникален для этой таблицы (хотелось бы сделать ее PK, эх)</t>
+  </si>
+  <si>
     <t>кто предлагает. Указываем по уровню лояльности</t>
   </si>
   <si>
@@ -589,140 +655,368 @@
     <t>text</t>
   </si>
   <si>
+    <t>bladed_weapons</t>
+  </si>
+  <si>
+    <t>weapons</t>
+  </si>
+  <si>
+    <t>TODO... гранаты, разгрузки, бронечехлы, рюкзаки, шлема, наушники, очки, маски, повязки, инъекторы</t>
+  </si>
+  <si>
+    <t>bullets</t>
+  </si>
+  <si>
+    <t>mods</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>specs</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>containers</t>
+  </si>
+  <si>
+    <t>keys</t>
+  </si>
+  <si>
+    <t>armors</t>
+  </si>
+  <si>
+    <t>TODO... создать сущность, описывающая свойства из этой категории</t>
+  </si>
+  <si>
+    <t>таблица с торговцами</t>
+  </si>
+  <si>
+    <t>trader_loyalty</t>
+  </si>
+  <si>
+    <t>таблица хранящая информацию о лояльности торговцев</t>
+  </si>
+  <si>
+    <t>items_unlocking_purchase</t>
+  </si>
+  <si>
+    <t>таблица с доступными предметами к покупке после квеста</t>
+  </si>
+  <si>
+    <t>items_unlocking_barter</t>
+  </si>
+  <si>
+    <t>таблица с доступными предметами к бартеру после квеста</t>
+  </si>
+  <si>
+    <t>таблица с свойствами холодного оружия</t>
+  </si>
+  <si>
+    <t>in_raid</t>
+  </si>
+  <si>
+    <t>trader_name</t>
+  </si>
+  <si>
+    <t>loyalty_level</t>
+  </si>
+  <si>
+    <t>min_loyalty</t>
+  </si>
+  <si>
+    <t>min_turnover_amount</t>
+  </si>
+  <si>
+    <t>unlocked_in_quest</t>
+  </si>
+  <si>
+    <t>hit_radius</t>
+  </si>
+  <si>
+    <t>chopping_damage</t>
+  </si>
+  <si>
+    <t>piercing_damage</t>
+  </si>
+  <si>
+    <t>special</t>
+  </si>
+  <si>
+    <t>имя торговца</t>
+  </si>
+  <si>
+    <t>иконка торговца</t>
+  </si>
+  <si>
+    <t>встретить только в рейде</t>
+  </si>
+  <si>
+    <t>уровень лояльности</t>
+  </si>
+  <si>
+    <t>с каким торговцем связан LL</t>
+  </si>
+  <si>
+    <t>минимальный уровень</t>
+  </si>
+  <si>
+    <t>минимальная лояльность</t>
+  </si>
+  <si>
+    <t>минимальный оборот средств</t>
+  </si>
+  <si>
+    <t>нужно ли открывать по квесту</t>
+  </si>
+  <si>
+    <t>с каким квестом связан</t>
+  </si>
+  <si>
+    <t>радиус удара</t>
+  </si>
+  <si>
+    <t>урон от рубящего</t>
+  </si>
+  <si>
+    <t>урон от колющего</t>
+  </si>
+  <si>
+    <t>особенное</t>
+  </si>
+  <si>
+    <t>торговцев немного, поэтому их имена можно использовать в качестве PK</t>
+  </si>
+  <si>
+    <t>да, смотрителя и водителя БТР сложно назвать торговцами, но они выдают квесты, а также на будущее будет запас, вдруг они не только будут выдавать квесты и оказывать услуги</t>
+  </si>
+  <si>
+    <t>опишем как id, чтобы удобнее было условия разблокировки. Благо условия разблокировки простые, нужно открыть за выполнение квестов, а повышать по простой схеме: min_level AND min_loyalty AND min_turnover_amount</t>
+  </si>
+  <si>
+    <t>проблема в том, что есть 3 типа торговцев: классическая LL (1..3 и prime), упрощенная (у скупщика, 1 и prime) и вообще без репутации (ни на что не влияет, записей о них здесь делать не нужно)</t>
+  </si>
+  <si>
+    <t>тут просто, уровней 1..3 и prime, для простоты назовем prime LL просто 4</t>
+  </si>
+  <si>
+    <t>если уровень не нужен, то просто 0</t>
+  </si>
+  <si>
+    <t>если не нужен, то просто 0</t>
+  </si>
+  <si>
+    <t>да, не все торговцы доступны сразу по 1LL, некоторых нужно открывать по сюжетному квесту "Тур", либо выполняя какой-то побочный квест (Легкие деньги часть 1 на Рефа LL1, Поручение на Егеря LL1 и Новое знакомство на Смотрителя)</t>
+  </si>
+  <si>
+    <t>ID берем из items_purchase</t>
+  </si>
+  <si>
+    <t>берем с таблицы лояльности</t>
+  </si>
+  <si>
+    <t>какой квест разблокирует бартер</t>
+  </si>
+  <si>
+    <t>ID берем из items_barter поле group</t>
+  </si>
+  <si>
+    <t>какой квест разблокировывает бартер</t>
+  </si>
+  <si>
+    <t>этот столбец будет PK и FK одновременно</t>
+  </si>
+  <si>
+    <t>есть особенные дебаффы, которое может наложить это оружие (кувалда Тагиллы, нож сектанта)</t>
+  </si>
+  <si>
+    <t>таблица огнестрельного оружия</t>
+  </si>
+  <si>
+    <t>таблица патронов</t>
+  </si>
+  <si>
+    <t>foods</t>
+  </si>
+  <si>
+    <t>таблица с едой</t>
+  </si>
+  <si>
+    <t>ergonomic</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>signting_range</t>
+  </si>
+  <si>
+    <t>vertical_recoil</t>
+  </si>
+  <si>
+    <t>horizontal_recoil</t>
+  </si>
+  <si>
+    <t>initial_velocity</t>
+  </si>
+  <si>
+    <t>firemode</t>
+  </si>
+  <si>
+    <t>caliber</t>
+  </si>
+  <si>
+    <t>firerate</t>
+  </si>
+  <si>
+    <t>effective_firerange</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>count_of_elements</t>
+  </si>
+  <si>
+    <t>bullet_speed</t>
+  </si>
+  <si>
+    <t>recoil</t>
+  </si>
+  <si>
+    <t>armor_penetration</t>
+  </si>
+  <si>
+    <t>severe_bleeding</t>
+  </si>
+  <si>
+    <t>minor_bleeding</t>
+  </si>
+  <si>
+    <t>duration_of_use</t>
+  </si>
+  <si>
+    <t>hydration</t>
+  </si>
+  <si>
+    <t>energy</t>
+  </si>
+  <si>
+    <t>ID оружия</t>
+  </si>
+  <si>
+    <t>тип оружия</t>
+  </si>
+  <si>
+    <t>эргономика</t>
+  </si>
+  <si>
+    <t>точность</t>
+  </si>
+  <si>
+    <t>прицельная дальность</t>
+  </si>
+  <si>
+    <t>вертикальная отдача</t>
+  </si>
+  <si>
+    <t>горизонтальная отдача</t>
+  </si>
+  <si>
+    <t>начальная скорость</t>
+  </si>
+  <si>
+    <t>режимы огня</t>
+  </si>
+  <si>
+    <t>калибр</t>
+  </si>
+  <si>
+    <t>скорострельность</t>
+  </si>
+  <si>
+    <t>эффективная дальность</t>
+  </si>
+  <si>
+    <t>особенные свойства</t>
+  </si>
+  <si>
+    <t>ID патрона</t>
+  </si>
+  <si>
+    <t>урон</t>
+  </si>
+  <si>
+    <t>количество элементов</t>
+  </si>
+  <si>
+    <t>скорость пули</t>
+  </si>
+  <si>
+    <t>отдача</t>
+  </si>
+  <si>
+    <t>бронепробитие</t>
+  </si>
+  <si>
+    <t>вероятность тяжелого кровотечения</t>
+  </si>
+  <si>
+    <t>вероятность легкого кровотечения</t>
+  </si>
+  <si>
+    <t>ID еды</t>
+  </si>
+  <si>
+    <t>время использования</t>
+  </si>
+  <si>
+    <t>гидрация</t>
+  </si>
+  <si>
+    <t>энергия</t>
+  </si>
+  <si>
+    <t>этот тип нужен для простой сортировки оружия по категориям</t>
+  </si>
+  <si>
+    <t>можно описать так, ОД, АТ, ОД/АТ, ОД/ОЧ, ОД/ОЧ/АТ. Других режимов не бывает</t>
+  </si>
+  <si>
+    <t>просто числом описать нельзя, есть специфичные калибры (7.62x39, 7.62x51, 7.62x54R и т.д.)</t>
+  </si>
+  <si>
+    <t>насколько я знаю, их нет, но лучше пусть будут</t>
+  </si>
+  <si>
+    <t>да, калибр указан в названии, но калибр требует группировки</t>
+  </si>
+  <si>
+    <t>сколько в одном патроне поражающих элементов. null будет считаться, что поражающих эл-ов 1</t>
+  </si>
+  <si>
+    <t>измеряется в процентах, но это проще учитывать в режиме сборки</t>
+  </si>
+  <si>
+    <t>стоит иметь в виду, что это непонятное двухзначное число читается по принципу: десяток -- какой класс брони гарантированно пробьет, единица -- с какой вероятностью пробьет класс выше</t>
+  </si>
+  <si>
     <t>TODO... описать каждую категорию</t>
   </si>
   <si>
-    <t>TODO... создать сущность, описывающая свойства из этой категории</t>
-  </si>
-  <si>
-    <t>bladed_weapons</t>
-  </si>
-  <si>
-    <t>weapons</t>
-  </si>
-  <si>
-    <t>bullets</t>
-  </si>
-  <si>
-    <t>mods</t>
-  </si>
-  <si>
-    <t>specs</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>medicine</t>
-  </si>
-  <si>
-    <t>containers</t>
-  </si>
-  <si>
-    <t>keys</t>
-  </si>
-  <si>
-    <t>armors</t>
-  </si>
-  <si>
-    <t>таблица с торговцами</t>
-  </si>
-  <si>
-    <t>trader_loyalty</t>
-  </si>
-  <si>
-    <t>таблица хранящая информацию о лояльности торговцев</t>
-  </si>
-  <si>
-    <t>items_unlocking_purchase</t>
-  </si>
-  <si>
-    <t>таблица с доступными предметами к покупке после квеста</t>
-  </si>
-  <si>
-    <t>in_raid</t>
-  </si>
-  <si>
-    <t>trader_name</t>
-  </si>
-  <si>
-    <t>loyalty_level</t>
-  </si>
-  <si>
-    <t>min_loyalty</t>
-  </si>
-  <si>
-    <t>min_turnover_amount</t>
-  </si>
-  <si>
-    <t>unlocked_in_quest</t>
-  </si>
-  <si>
-    <t>имя торговца</t>
-  </si>
-  <si>
-    <t>иконка торговца</t>
-  </si>
-  <si>
-    <t>встретить только в рейде</t>
-  </si>
-  <si>
-    <t>уровень лояльности</t>
-  </si>
-  <si>
-    <t>с каким торговцем связан LL</t>
-  </si>
-  <si>
-    <t>минимальный уровень</t>
-  </si>
-  <si>
-    <t>минимальная лояльность</t>
-  </si>
-  <si>
-    <t>минимальный оборот средств</t>
-  </si>
-  <si>
-    <t>нужно ли открывать по квесту</t>
-  </si>
-  <si>
-    <t>с каким квестом связан</t>
-  </si>
-  <si>
-    <t>торговцев немного, поэтому их имена можно использовать в качестве PK</t>
-  </si>
-  <si>
-    <t>да, смотрителя и водителя БТР сложно назвать торговцами, но они выдают квесты, а также на будущее будет запас, вдруг они не только будут выдавать квесты и оказывать услуги</t>
-  </si>
-  <si>
-    <t>опишем как id, чтобы удобнее было условия разблокировки. Благо условия разблокировки простые, нужно открыть за выполнение квестов, а повышать по простой схеме: min_level AND min_loyalty AND min_turnover_amount</t>
-  </si>
-  <si>
-    <t>проблема в том, что есть 3 типа торговцев: классическая LL (1..3 и prime), упрощенная (у скупщика, 1 и prime) и вообще без репутации (ни на что не влияет, записей о них здесь делать не нужно)</t>
-  </si>
-  <si>
-    <t>тут просто, уровней 1..3 и prime, для простоты назовем prime LL просто 4</t>
-  </si>
-  <si>
-    <t>если уровень не нужен, то просто 0</t>
-  </si>
-  <si>
-    <t>если не нужен, то просто 0</t>
-  </si>
-  <si>
-    <t>да, не все торговцы доступны сразу по 1LL, некоторых нужно открывать по сюжетному квесту "Тур", либо выполняя какой-то побочный квест (Легкие деньги часть 1 на Рефа LL1, Поручение на Егеря LL1 и Новое знакомство на Смотрителя)</t>
-  </si>
-  <si>
-    <t>берем с таблицы лояльности</t>
-  </si>
-  <si>
-    <t>какой квест разблокировывает бартер</t>
+    <t>TODO... структура модификаций и сборок (будет очень весело), БД должна быть заполнена</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -758,10 +1052,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="6">
@@ -923,7 +1226,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -951,6 +1254,9 @@
     <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -997,9 +1303,6 @@
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1034,7 +1337,10 @@
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1049,13 +1355,67 @@
     <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="14" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1279,29 +1639,33 @@
     <col customWidth="1" min="2" max="2" width="32.5"/>
     <col customWidth="1" min="3" max="3" width="30.0"/>
     <col customWidth="1" min="4" max="4" width="19.38"/>
-    <col customWidth="1" min="5" max="5" width="32.25"/>
+    <col customWidth="1" min="5" max="5" width="36.25"/>
     <col customWidth="1" min="6" max="6" width="29.0"/>
     <col customWidth="1" min="7" max="7" width="20.63"/>
     <col customWidth="1" min="8" max="8" width="31.5"/>
     <col customWidth="1" min="9" max="9" width="22.88"/>
     <col customWidth="1" min="10" max="10" width="62.88"/>
     <col customWidth="1" min="11" max="11" width="34.5"/>
-    <col customWidth="1" min="12" max="12" width="24.25"/>
-    <col customWidth="1" min="13" max="13" width="21.88"/>
+    <col customWidth="1" min="12" max="12" width="32.0"/>
+    <col customWidth="1" min="13" max="13" width="27.25"/>
     <col customWidth="1" min="14" max="14" width="19.75"/>
-    <col customWidth="1" min="15" max="15" width="25.25"/>
-    <col customWidth="1" min="16" max="16" width="20.13"/>
+    <col customWidth="1" min="15" max="15" width="33.5"/>
+    <col customWidth="1" min="16" max="16" width="43.75"/>
     <col customWidth="1" min="17" max="17" width="26.38"/>
     <col customWidth="1" min="18" max="18" width="22.88"/>
     <col customWidth="1" min="19" max="19" width="18.63"/>
-    <col customWidth="1" min="20" max="20" width="31.88"/>
+    <col customWidth="1" min="20" max="20" width="26.25"/>
     <col customWidth="1" min="21" max="21" width="30.25"/>
-    <col customWidth="1" min="22" max="22" width="23.5"/>
-    <col customWidth="1" min="23" max="23" width="28.25"/>
-    <col customWidth="1" min="24" max="24" width="26.38"/>
-    <col customWidth="1" min="25" max="25" width="18.88"/>
+    <col customWidth="1" min="22" max="22" width="28.13"/>
+    <col customWidth="1" min="23" max="23" width="38.5"/>
+    <col customWidth="1" min="24" max="24" width="28.88"/>
+    <col customWidth="1" min="25" max="25" width="27.88"/>
     <col customWidth="1" min="26" max="26" width="62.88"/>
-    <col customWidth="1" min="27" max="28" width="31.88"/>
+    <col customWidth="1" min="27" max="27" width="26.63"/>
+    <col customWidth="1" min="28" max="28" width="24.88"/>
+    <col customWidth="1" min="29" max="29" width="31.88"/>
+    <col customWidth="1" min="30" max="30" width="24.38"/>
+    <col customWidth="1" min="31" max="31" width="31.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1338,1416 +1702,2261 @@
         <v>7</v>
       </c>
       <c r="T1" s="4"/>
+      <c r="V1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="4"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>8</v>
-      </c>
       <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>21</v>
+      <c r="W2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="H3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="I3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="L3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="16"/>
+      <c r="M3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="S4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA4" s="16"/>
-      <c r="AB4" s="16"/>
+      <c r="A4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="T5" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA5" s="16"/>
-      <c r="AB5" s="16"/>
+      <c r="A5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="T5" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y5" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
     </row>
     <row r="6">
-      <c r="A6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
+      <c r="A6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>57</v>
+      <c r="A7" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="F7" s="25" t="s">
-        <v>58</v>
+      <c r="F7" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="4"/>
-      <c r="M7" s="26" t="s">
-        <v>60</v>
+      <c r="M7" s="27" t="s">
+        <v>77</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="4"/>
       <c r="T7" s="7" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="4"/>
       <c r="Y7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z7" s="27" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="Z7" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="U8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="T8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="V8" s="7" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="9" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="AA8" s="31"/>
       <c r="AB8" s="31"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="T9" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>93</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="AA9" s="31"/>
       <c r="AB9" s="31"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="31"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="T10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="V10" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z10" s="12" t="s">
-        <v>39</v>
+      <c r="A10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="V10" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z10" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="AA10" s="31"/>
       <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="31"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="P11" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q11" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="R11" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="V11" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="W11" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y11" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z11" s="17" t="s">
-        <v>51</v>
+      <c r="A11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q11" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="R11" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="W11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z11" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="AA11" s="31"/>
       <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="31"/>
     </row>
     <row r="12">
       <c r="C12" s="32" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="J12" s="33" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="O12" s="33" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="V12" s="33" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="Z12" s="33" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="AA12" s="34"/>
       <c r="AB12" s="34"/>
+      <c r="AC12" s="34"/>
+      <c r="AD12" s="34"/>
+      <c r="AE12" s="34"/>
     </row>
     <row r="13">
       <c r="C13" s="35" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J13" s="36" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="O13" s="36" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="V13" s="36" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="Z13" s="36" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AA13" s="34"/>
       <c r="AB13" s="34"/>
+      <c r="AC13" s="34"/>
+      <c r="AD13" s="34"/>
+      <c r="AE13" s="34"/>
     </row>
     <row r="14">
       <c r="C14" s="35" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="J14" s="36" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="O14" s="36" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="V14" s="36" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="Z14" s="37" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="AA14" s="34"/>
       <c r="AB14" s="34"/>
+      <c r="AC14" s="34"/>
+      <c r="AD14" s="34"/>
+      <c r="AE14" s="34"/>
     </row>
     <row r="15">
       <c r="C15" s="35" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
+        <v>145</v>
+      </c>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
     </row>
     <row r="16">
       <c r="C16" s="35" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="O16" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
+        <v>148</v>
+      </c>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
     </row>
     <row r="17">
       <c r="C17" s="35" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J17" s="36" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="O17" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
+        <v>151</v>
+      </c>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
     </row>
     <row r="18">
       <c r="C18" s="35" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="O18" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
+        <v>154</v>
+      </c>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
     </row>
     <row r="19">
       <c r="C19" s="35" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="O19" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
+        <v>155</v>
+      </c>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
     </row>
     <row r="20">
       <c r="C20" s="35" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="O20" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA20" s="16"/>
-      <c r="AB20" s="16"/>
+        <v>157</v>
+      </c>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
     </row>
     <row r="21">
       <c r="C21" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16"/>
+        <v>158</v>
+      </c>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
     </row>
     <row r="22">
       <c r="C22" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA22" s="16"/>
-      <c r="AB22" s="16"/>
+        <v>159</v>
+      </c>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
     </row>
     <row r="23">
       <c r="AB23" s="39"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C24" s="4"/>
       <c r="E24" s="7" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="4"/>
-      <c r="L24" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="4"/>
-      <c r="R24" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="4"/>
+      <c r="N24" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="4"/>
+      <c r="T24" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>167</v>
+      </c>
       <c r="V24" s="3"/>
-      <c r="W24" s="4"/>
-      <c r="Y24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="4"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="4"/>
+      <c r="AA24" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB24" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>156</v>
+        <v>172</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>17</v>
+        <v>174</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>159</v>
+        <v>14</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>160</v>
+        <v>175</v>
+      </c>
+      <c r="X25" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z25" s="7" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="AA25" s="7" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="AB25" s="7" t="s">
-        <v>20</v>
+        <v>89</v>
+      </c>
+      <c r="AC25" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE25" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>25</v>
+      <c r="A26" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="J26" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="R26" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="S26" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="V26" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y26" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z26" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA26" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB26" s="41" t="s">
-        <v>174</v>
+        <v>185</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="L26" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="T26" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="U26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="V26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W26" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="X26" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y26" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA26" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB26" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC26" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD26" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE26" s="42" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="B27" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="R27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="S27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="T27" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="U27" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y27" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z27" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA27" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="AB27" s="12" t="s">
-        <v>189</v>
+      <c r="A27" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="R27" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="T27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="V27" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="W27" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="X27" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA27" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC27" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD27" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE27" s="13" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="L28" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="M28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="O28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="P28" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="R28" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="S28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="T28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="U28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="V28" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="W28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y28" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA28" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB28" s="17" t="s">
-        <v>53</v>
+      <c r="A28" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="N28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="U28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="W28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="X28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE28" s="18" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31"/>
-      <c r="B29" s="44"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="31"/>
-      <c r="D29" s="16"/>
+      <c r="D29" s="17"/>
       <c r="E29" s="31"/>
       <c r="F29" s="31"/>
       <c r="G29" s="31"/>
-      <c r="H29" s="31" t="s">
-        <v>192</v>
+      <c r="H29" s="46" t="s">
+        <v>214</v>
       </c>
       <c r="I29" s="31"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="V29" s="33" t="s">
-        <v>119</v>
+      <c r="L29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="W29" s="33" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="31"/>
-      <c r="B30" s="44"/>
+      <c r="B30" s="45"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="16"/>
+      <c r="D30" s="17"/>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="I30" s="31"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="V30" s="36" t="s">
-        <v>124</v>
+      <c r="H30" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="L30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="W30" s="36" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="31"/>
-      <c r="B31" s="44"/>
+      <c r="B31" s="45"/>
       <c r="C31" s="31"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="H31" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="I31" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="J31" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="V31" s="36" t="s">
-        <v>128</v>
+      <c r="D31" s="17"/>
+      <c r="G31" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="L31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="W31" s="36" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="31"/>
-      <c r="B32" s="44"/>
+      <c r="B32" s="45"/>
       <c r="C32" s="31"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="H32" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="I32" s="31"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="V32" s="37" t="s">
-        <v>132</v>
+      <c r="D32" s="17"/>
+      <c r="H32" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="W32" s="37" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="31"/>
-      <c r="B33" s="44"/>
+      <c r="B33" s="45"/>
       <c r="C33" s="31"/>
-      <c r="D33" s="16"/>
+      <c r="D33" s="17"/>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="AA33" s="16"/>
-      <c r="AB33" s="16"/>
+      <c r="H33" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="I33" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="49"/>
+      <c r="U33" s="49"/>
+      <c r="AA33" s="17"/>
+      <c r="AB33" s="17"/>
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="N34" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="4"/>
-      <c r="U34" s="45"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="H34" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA34" s="17"/>
+      <c r="AB34" s="17"/>
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I35" s="7" t="s">
+      <c r="D35" s="17"/>
+      <c r="H35" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17"/>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="17"/>
+      <c r="H36" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA36" s="17"/>
+      <c r="AB36" s="17"/>
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="17"/>
+      <c r="H37" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="17"/>
+      <c r="H38" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="31"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="51"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="53"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="4"/>
+      <c r="S40" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="T40" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="4"/>
+      <c r="Y40" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z40" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="4"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="L41" s="23"/>
+      <c r="M41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="S41" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="T41" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="U41" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="V41" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="W41" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y41" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z41" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA41" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB41" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC41" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D42" s="17"/>
+      <c r="E42" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="L42" s="23"/>
+      <c r="M42" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="N42" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O42" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="P42" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q42" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="S42" s="60" t="s">
+        <v>188</v>
+      </c>
+      <c r="T42" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="U42" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="V42" s="60" t="s">
+        <v>254</v>
+      </c>
+      <c r="W42" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y42" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z42" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="AA42" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB42" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC42" s="42" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="B43" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="L43" s="23"/>
+      <c r="M43" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="O43" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="P43" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q43" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="S43" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="T43" s="62" t="s">
+        <v>270</v>
+      </c>
+      <c r="U43" s="61" t="s">
+        <v>268</v>
+      </c>
+      <c r="V43" s="60" t="s">
+        <v>271</v>
+      </c>
+      <c r="W43" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y43" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="Z43" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA43" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB43" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC43" s="13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="B44" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="17"/>
+      <c r="E44" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="L44" s="23"/>
+      <c r="M44" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="O44" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="P44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="S44" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="T44" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="U44" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="V44" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="W44" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y44" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z44" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB44" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC44" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="L35" s="22"/>
-      <c r="M35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O35" s="47" t="s">
-        <v>157</v>
-      </c>
-      <c r="P35" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="U35" s="45"/>
-      <c r="AA35" s="16"/>
-      <c r="AB35" s="16"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="s">
+    </row>
+    <row r="45">
+      <c r="A45" s="31"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="51"/>
+      <c r="M45" s="31"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="45"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="53"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="52"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="31"/>
+      <c r="Z45" s="31"/>
+      <c r="AA45" s="31"/>
+      <c r="AB45" s="31"/>
+      <c r="AC45" s="31"/>
+      <c r="AD45" s="17"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B36" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" s="12" t="s">
+      <c r="B46" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="L36" s="22"/>
-      <c r="M36" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="O36" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="P36" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q36" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="U36" s="45"/>
-      <c r="AA36" s="16"/>
-      <c r="AB36" s="16"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B37" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="K37" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="L37" s="22"/>
-      <c r="M37" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O37" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="P37" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q37" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="U37" s="45"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="B38" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="I38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="L38" s="22"/>
-      <c r="M38" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="N38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="O38" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="P38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q38" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="U38" s="45"/>
+      <c r="P46" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="31"/>
+      <c r="AA46" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB46" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC46" s="3"/>
+      <c r="AD46" s="3"/>
+      <c r="AE46" s="4"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="N47" s="31"/>
+      <c r="O47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P47" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q47" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="R47" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="S47" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="T47" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="U47" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="V47" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="W47" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="X47" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="Y47" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="Z47" s="31"/>
+      <c r="AA47" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB47" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="AC47" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="AD47" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="AE47" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="E48" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="F48" s="42" t="s">
+        <v>303</v>
+      </c>
+      <c r="G48" s="42" t="s">
+        <v>304</v>
+      </c>
+      <c r="H48" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="I48" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="J48" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="K48" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="L48" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="M48" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N48" s="31"/>
+      <c r="O48" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="P48" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q48" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="R48" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="S48" s="62" t="s">
+        <v>314</v>
+      </c>
+      <c r="T48" s="62" t="s">
+        <v>301</v>
+      </c>
+      <c r="U48" s="62" t="s">
+        <v>315</v>
+      </c>
+      <c r="V48" s="62" t="s">
+        <v>316</v>
+      </c>
+      <c r="W48" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="X48" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="Y48" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="Z48" s="31"/>
+      <c r="AA48" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="AB48" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="AC48" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="AD48" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="AE48" s="42" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>323</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="K49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="N49" s="31"/>
+      <c r="O49" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="P49" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="R49" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="S49" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="T49" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="U49" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="V49" s="62" t="s">
+        <v>330</v>
+      </c>
+      <c r="W49" s="62" t="s">
+        <v>51</v>
+      </c>
+      <c r="X49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z49" s="31"/>
+      <c r="AA49" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="AB49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE49" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M50" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="N50" s="31"/>
+      <c r="O50" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="P50" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R50" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="S50" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="T50" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="U50" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="V50" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="W50" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="X50" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y50" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z50" s="31"/>
+      <c r="AA50" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE50" s="18" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="31"/>
+      <c r="B51" s="45" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="51"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="45"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="52"/>
+      <c r="T51" s="52"/>
+      <c r="U51" s="53"/>
+      <c r="V51" s="52"/>
+      <c r="W51" s="52"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="31"/>
+      <c r="Z51" s="31"/>
+      <c r="AA51" s="31"/>
+      <c r="AB51" s="31"/>
+      <c r="AC51" s="31"/>
+      <c r="AD51" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="M1:P1"/>
@@ -2755,15 +3964,21 @@
     <mergeCell ref="G7:K7"/>
     <mergeCell ref="N7:R7"/>
     <mergeCell ref="U7:W7"/>
-    <mergeCell ref="F34:K34"/>
-    <mergeCell ref="N34:Q34"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="F40:K40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="T40:W40"/>
+    <mergeCell ref="Z40:AC40"/>
+    <mergeCell ref="B46:M46"/>
+    <mergeCell ref="P46:Y46"/>
+    <mergeCell ref="AB46:AE46"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="S24:W24"/>
-    <mergeCell ref="Z24:AB24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="U24:Y24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="F24:L24"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/draft/database_eft.xlsx
+++ b/draft/database_eft.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="182">
-  <si>
-    <t>quest</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="405">
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>таблица со всеми квестами</t>
@@ -37,13 +37,25 @@
     <t>таблица отслеживания целей</t>
   </si>
   <si>
+    <t>trader_user_loyalty</t>
+  </si>
+  <si>
+    <t>таблица лояльности к торговцам</t>
+  </si>
+  <si>
+    <t>items_user</t>
+  </si>
+  <si>
+    <t>таблица найденых предметов</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <t>owner</t>
+    <t>trader</t>
   </si>
   <si>
     <t>description</t>
@@ -79,6 +91,15 @@
     <t>is_finished</t>
   </si>
   <si>
+    <t>loyalty</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>count_in_raid</t>
+  </si>
+  <si>
     <t>номер квеста</t>
   </si>
   <si>
@@ -130,10 +151,25 @@
     <t>выполнен ли?</t>
   </si>
   <si>
+    <t>торговец</t>
+  </si>
+  <si>
+    <t>лояльность к этому торговцу</t>
+  </si>
+  <si>
+    <t>предмет</t>
+  </si>
+  <si>
+    <t>количество</t>
+  </si>
+  <si>
+    <t>количество с "найдено в рейде"</t>
+  </si>
+  <si>
     <t>без комментариев</t>
   </si>
   <si>
-    <t>не требует сложной структуры, просто надо записывать правильно имя торговцев</t>
+    <t>не требует сложной структуры, от лояльности не зависит</t>
   </si>
   <si>
     <t>Тупо текст нельзя хранить, поскольку нужны скрины, возможно видео</t>
@@ -163,6 +199,12 @@
     <t>без комментариев. Также false, если null</t>
   </si>
   <si>
+    <t>да, этот столбец будет PK и FK одновременно</t>
+  </si>
+  <si>
+    <t>по умолчанию лояльность 0.00, либо +N на старте в зависимости от издания</t>
+  </si>
+  <si>
     <t>int not null primary key</t>
   </si>
   <si>
@@ -181,6 +223,15 @@
     <t>bool</t>
   </si>
   <si>
+    <t>text not null primary key FK</t>
+  </si>
+  <si>
+    <t>float not null</t>
+  </si>
+  <si>
+    <t>int not null primary key FK</t>
+  </si>
+  <si>
     <t>quest_available</t>
   </si>
   <si>
@@ -355,9 +406,6 @@
     <t>put_item</t>
   </si>
   <si>
-    <t>item</t>
-  </si>
-  <si>
     <t>competed</t>
   </si>
   <si>
@@ -439,12 +487,12 @@
     <t>up_level</t>
   </si>
   <si>
-    <t>TODO... таблица бартера</t>
-  </si>
-  <si>
     <t>kill_zryachy</t>
   </si>
   <si>
+    <t>min_fence_loyalty</t>
+  </si>
+  <si>
     <t>map</t>
   </si>
   <si>
@@ -469,13 +517,25 @@
     <t>таблица ценами продажи торговцев</t>
   </si>
   <si>
+    <t>items_barter</t>
+  </si>
+  <si>
+    <t>таблица с бартером</t>
+  </si>
+  <si>
     <t>image</t>
   </si>
   <si>
     <t>max_pmc</t>
   </si>
   <si>
-    <t>trader</t>
+    <t>unlock_flea_market</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>enable_drop</t>
   </si>
   <si>
     <t>price</t>
@@ -484,6 +544,12 @@
     <t>valuta</t>
   </si>
   <si>
+    <t>max_count</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
     <t>Название карты</t>
   </si>
   <si>
@@ -502,12 +568,18 @@
     <t>тип предмета</t>
   </si>
   <si>
+    <t>с какого уровня доступен на барахолке</t>
+  </si>
+  <si>
+    <t>масса предмета</t>
+  </si>
+  <si>
+    <t>сколько можно выбросить в рейде</t>
+  </si>
+  <si>
     <t>ID предложения</t>
   </si>
   <si>
-    <t>торговец</t>
-  </si>
-  <si>
     <t>цена закупки</t>
   </si>
   <si>
@@ -517,6 +589,12 @@
     <t>цена продажи</t>
   </si>
   <si>
+    <t>сколько можно купить за 1 завоз</t>
+  </si>
+  <si>
+    <t>номер группы</t>
+  </si>
+  <si>
     <t>Избыточно будет если сделать ID как уникальный ключ</t>
   </si>
   <si>
@@ -529,6 +607,15 @@
     <t>у каждой категории предметов есть свои категории свойств (как у бутылки воды может быть 1.42 MOA?)</t>
   </si>
   <si>
+    <t>вот чем и грешат старые справочники. До релиза было просто: барахолка доступна только с уровня N, и она давала доступ абсолютно ко всем предметам. Теперь же мало того, что не каждый предмет доступен на барахолке, так еще и становится доступен с уровня N. Можно было привязать доступность к категории предмета, но некоторые предметы -- исключение из правил. Например, ключи можно покупать только с 25 уровня, но ключи от "меченок" доступны с 35 уровня, а танковый аккум хоть и относится к категории электроника (доступен с 20 уровня), но доступен с 40 уровня. Если поле на записи здесь пустое, значит предмет не доступен на барахолке, потому что сама барахолка открывается с 15 уровня</t>
+  </si>
+  <si>
+    <t>единственное, что есть у каждого предмета. Есть специфичные предметы, которые не имеют массы</t>
+  </si>
+  <si>
+    <t>если null, то в рейде выбросить нельзя</t>
+  </si>
+  <si>
     <t>поскольку один и тот же предмет могут купить разные торговцы за разную стоимость, поэтому идея "1 item = 1 item_purchase" не подходит. Если цены нет, значит торговец не покупает</t>
   </si>
   <si>
@@ -541,10 +628,7 @@
     <t>да, пока тогровцы скупают за рубль, кроме миротворца, однако судя по развитию игры, а также по наличию других валют, лучше сделать этот пункт</t>
   </si>
   <si>
-    <t>аналогично с itmes_purchase</t>
-  </si>
-  <si>
-    <t>тот, кто продает этот предмет</t>
+    <t>тот, кто продает этот предмет. Указываем по уровню лояльности</t>
   </si>
   <si>
     <t>то, за сколько продает торговец</t>
@@ -553,17 +637,602 @@
     <t>здесь проще, чем в items_purchase, потому что торговцы часто продают по разнообразной валюте</t>
   </si>
   <si>
+    <t>можно было бы привязать ID предложения к ID item, но торговец имеет наглость просить за 1 предмет несколько разных предметов</t>
+  </si>
+  <si>
+    <t>есть проблема в том, что у одного торговца есть несколько разных бартеров, поэтому идея привязывать 1 одному предмету 1 бартер -- не лучшая идея. даже если бартер уникальный, у нее все равно номер группы уникален для этой таблицы (хотелось бы сделать ее PK, эх)</t>
+  </si>
+  <si>
+    <t>кто предлагает. Указываем по уровню лояльности</t>
+  </si>
+  <si>
+    <t>торговец может требовать за 1 предмет несколько разных, но правильней говорить несколько категорий предметов. Например, Миротворец 2LL требует за защищенный кейс Бета 1 танковый аккум, 5 военных кабелей, 3 виртекса и 3 иридиума</t>
+  </si>
+  <si>
     <t>text not null primary key</t>
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>bladed_weapons</t>
+  </si>
+  <si>
+    <t>weapons</t>
+  </si>
+  <si>
+    <t>bullets</t>
+  </si>
+  <si>
+    <t>mods</t>
+  </si>
+  <si>
+    <t>specs</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>containers</t>
+  </si>
+  <si>
+    <t>keys</t>
+  </si>
+  <si>
+    <t>armor_vests</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>grenades</t>
+  </si>
+  <si>
+    <t>chest_rigs</t>
+  </si>
+  <si>
+    <t>headwears</t>
+  </si>
+  <si>
+    <t>backpacks</t>
+  </si>
+  <si>
+    <t>earpieces</t>
+  </si>
+  <si>
+    <t>eyewears</t>
+  </si>
+  <si>
+    <t>face_covers</t>
+  </si>
+  <si>
+    <t>armbands</t>
+  </si>
+  <si>
+    <t>injectors</t>
+  </si>
+  <si>
+    <t>TODO... создать сущность, описывающая свойства из этой категории</t>
+  </si>
+  <si>
+    <t>таблица с торговцами</t>
+  </si>
+  <si>
+    <t>trader_loyalty</t>
+  </si>
+  <si>
+    <t>таблица хранящая информацию о лояльности торговцев</t>
+  </si>
+  <si>
+    <t>items_unlocking_purchase</t>
+  </si>
+  <si>
+    <t>таблица с доступными предметами к покупке после квеста</t>
+  </si>
+  <si>
+    <t>items_unlocking_barter</t>
+  </si>
+  <si>
+    <t>таблица с доступными предметами к бартеру после квеста</t>
+  </si>
+  <si>
+    <t>таблица с свойствами холодного оружия</t>
+  </si>
+  <si>
+    <t>in_raid</t>
+  </si>
+  <si>
+    <t>trader_name</t>
+  </si>
+  <si>
+    <t>loyalty_level</t>
+  </si>
+  <si>
+    <t>min_loyalty</t>
+  </si>
+  <si>
+    <t>min_turnover_amount</t>
+  </si>
+  <si>
+    <t>unlocked_in_quest</t>
+  </si>
+  <si>
+    <t>hit_radius</t>
+  </si>
+  <si>
+    <t>chopping_damage</t>
+  </si>
+  <si>
+    <t>piercing_damage</t>
+  </si>
+  <si>
+    <t>special</t>
+  </si>
+  <si>
+    <t>имя торговца</t>
+  </si>
+  <si>
+    <t>иконка торговца</t>
+  </si>
+  <si>
+    <t>встретить только в рейде</t>
+  </si>
+  <si>
+    <t>уровень лояльности</t>
+  </si>
+  <si>
+    <t>с каким торговцем связан LL</t>
+  </si>
+  <si>
+    <t>минимальный уровень</t>
+  </si>
+  <si>
+    <t>минимальная лояльность</t>
+  </si>
+  <si>
+    <t>минимальный оборот средств</t>
+  </si>
+  <si>
+    <t>нужно ли открывать по квесту</t>
+  </si>
+  <si>
+    <t>с каким квестом связан</t>
+  </si>
+  <si>
+    <t>радиус удара</t>
+  </si>
+  <si>
+    <t>урон от рубящего</t>
+  </si>
+  <si>
+    <t>урон от колющего</t>
+  </si>
+  <si>
+    <t>особенное</t>
+  </si>
+  <si>
+    <t>торговцев немного, поэтому их имена можно использовать в качестве PK</t>
+  </si>
+  <si>
+    <t>да, смотрителя и водителя БТР сложно назвать торговцами, но они выдают квесты, а также на будущее будет запас, вдруг они не только будут выдавать квесты и оказывать услуги</t>
+  </si>
+  <si>
+    <t>опишем как id, чтобы удобнее было условия разблокировки. Благо условия разблокировки простые, нужно открыть за выполнение квестов, а повышать по простой схеме: min_level AND min_loyalty AND min_turnover_amount</t>
+  </si>
+  <si>
+    <t>проблема в том, что есть 3 типа торговцев: классическая LL (1..3 и prime), упрощенная (у скупщика, 1 и prime) и вообще без репутации (ни на что не влияет, записей о них здесь делать не нужно)</t>
+  </si>
+  <si>
+    <t>тут просто, уровней 1..3 и prime, для простоты назовем prime LL просто 4</t>
+  </si>
+  <si>
+    <t>если уровень не нужен, то просто 0</t>
+  </si>
+  <si>
+    <t>если не нужен, то просто 0</t>
+  </si>
+  <si>
+    <t>да, не все торговцы доступны сразу по 1LL, некоторых нужно открывать по сюжетному квесту "Тур", либо выполняя какой-то побочный квест (Легкие деньги часть 1 на Рефа LL1, Поручение на Егеря LL1 и Новое знакомство на Смотрителя)</t>
+  </si>
+  <si>
+    <t>ID берем из items_purchase</t>
+  </si>
+  <si>
+    <t>берем с таблицы лояльности</t>
+  </si>
+  <si>
+    <t>какой квест разблокирует бартер</t>
+  </si>
+  <si>
+    <t>ID берем из items_barter поле group</t>
+  </si>
+  <si>
+    <t>какой квест разблокировывает бартер</t>
+  </si>
+  <si>
+    <t>этот столбец будет PK и FK одновременно</t>
+  </si>
+  <si>
+    <t>есть особенные дебаффы, которое может наложить это оружие (кувалда Тагиллы, нож сектанта)</t>
+  </si>
+  <si>
+    <t>таблица огнестрельного оружия</t>
+  </si>
+  <si>
+    <t>таблица патронов</t>
+  </si>
+  <si>
+    <t>foods</t>
+  </si>
+  <si>
+    <t>таблица с едой</t>
+  </si>
+  <si>
+    <t>ergonomic</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>signting_range</t>
+  </si>
+  <si>
+    <t>vertical_recoil</t>
+  </si>
+  <si>
+    <t>horizontal_recoil</t>
+  </si>
+  <si>
+    <t>initial_velocity</t>
+  </si>
+  <si>
+    <t>firemode</t>
+  </si>
+  <si>
+    <t>caliber</t>
+  </si>
+  <si>
+    <t>firerate</t>
+  </si>
+  <si>
+    <t>effective_firerange</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>count_of_elements</t>
+  </si>
+  <si>
+    <t>bullet_speed</t>
+  </si>
+  <si>
+    <t>recoil</t>
+  </si>
+  <si>
+    <t>armor_penetration</t>
+  </si>
+  <si>
+    <t>severe_bleeding</t>
+  </si>
+  <si>
+    <t>minor_bleeding</t>
+  </si>
+  <si>
+    <t>duration_of_use</t>
+  </si>
+  <si>
+    <t>hydration</t>
+  </si>
+  <si>
+    <t>energy</t>
+  </si>
+  <si>
+    <t>ID оружия</t>
+  </si>
+  <si>
+    <t>тип оружия</t>
+  </si>
+  <si>
+    <t>эргономика</t>
+  </si>
+  <si>
+    <t>точность</t>
+  </si>
+  <si>
+    <t>прицельная дальность</t>
+  </si>
+  <si>
+    <t>вертикальная отдача</t>
+  </si>
+  <si>
+    <t>горизонтальная отдача</t>
+  </si>
+  <si>
+    <t>начальная скорость</t>
+  </si>
+  <si>
+    <t>режимы огня</t>
+  </si>
+  <si>
+    <t>калибр</t>
+  </si>
+  <si>
+    <t>скорострельность</t>
+  </si>
+  <si>
+    <t>эффективная дальность</t>
+  </si>
+  <si>
+    <t>особенные свойства</t>
+  </si>
+  <si>
+    <t>ID патрона</t>
+  </si>
+  <si>
+    <t>урон</t>
+  </si>
+  <si>
+    <t>количество элементов</t>
+  </si>
+  <si>
+    <t>скорость пули</t>
+  </si>
+  <si>
+    <t>отдача</t>
+  </si>
+  <si>
+    <t>бронепробитие</t>
+  </si>
+  <si>
+    <t>вероятность тяжелого кровотечения</t>
+  </si>
+  <si>
+    <t>вероятность легкого кровотечения</t>
+  </si>
+  <si>
+    <t>ID еды</t>
+  </si>
+  <si>
+    <t>время использования</t>
+  </si>
+  <si>
+    <t>гидрация</t>
+  </si>
+  <si>
+    <t>энергия</t>
+  </si>
+  <si>
+    <t>этот тип нужен для простой сортировки оружия по категориям</t>
+  </si>
+  <si>
+    <t>можно описать так, ОД, АТ, ОД/АТ, ОД/ОЧ, ОД/ОЧ/АТ. Других режимов не бывает</t>
+  </si>
+  <si>
+    <t>просто числом описать нельзя, есть специфичные калибры (7.62x39, 7.62x51, 7.62x54R и т.д.)</t>
+  </si>
+  <si>
+    <t>насколько я знаю, их нет, но лучше пусть будут</t>
+  </si>
+  <si>
+    <t>да, калибр указан в названии, но калибр требует группировки</t>
+  </si>
+  <si>
+    <t>сколько в одном патроне поражающих элементов. null будет считаться, что поражающих эл-ов 1</t>
+  </si>
+  <si>
+    <t>измеряется в процентах, но это проще учитывать в режиме сборки</t>
+  </si>
+  <si>
+    <t>стоит иметь в виду, что это непонятное двухзначное число читается по принципу: десяток -- какой класс брони гарантированно пробьет, единица -- с какой вероятностью пробьет класс выше</t>
+  </si>
+  <si>
+    <t>TODO... описать каждую категорию</t>
+  </si>
+  <si>
+    <t>TODO... структура модификаций и сборок (будет очень весело), БД должна быть заполнена</t>
+  </si>
+  <si>
+    <t>таблица модов</t>
+  </si>
+  <si>
+    <t>таблица спец. предметов</t>
+  </si>
+  <si>
+    <t>таблица медицины</t>
+  </si>
+  <si>
+    <t>таблица контейнеров</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>relations</t>
+  </si>
+  <si>
+    <t>enable_to_raid</t>
+  </si>
+  <si>
+    <t>resource</t>
+  </si>
+  <si>
+    <t>healing</t>
+  </si>
+  <si>
+    <t>fracture</t>
+  </si>
+  <si>
+    <t>elimination_of_contusion</t>
+  </si>
+  <si>
+    <t>painkiller</t>
+  </si>
+  <si>
+    <t>contusion</t>
+  </si>
+  <si>
+    <t>surgery</t>
+  </si>
+  <si>
+    <t>is_shield</t>
+  </si>
+  <si>
+    <t>enable_categories</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>ID модификации</t>
+  </si>
+  <si>
+    <t>информация о модицикации</t>
+  </si>
+  <si>
+    <t>связь с другими предметами</t>
+  </si>
+  <si>
+    <t>использование в рейде</t>
+  </si>
+  <si>
+    <t>ресурс</t>
+  </si>
+  <si>
+    <t>лечение</t>
+  </si>
+  <si>
+    <t>устранение перелома</t>
+  </si>
+  <si>
+    <t>остановка тяжелого кровотечения</t>
+  </si>
+  <si>
+    <t>остановка легкого кровотечения</t>
+  </si>
+  <si>
+    <t>снятие контузии</t>
+  </si>
+  <si>
+    <t>устранение боли</t>
+  </si>
+  <si>
+    <t>контузия</t>
+  </si>
+  <si>
+    <t>хирургия</t>
+  </si>
+  <si>
+    <t>ID контейнера</t>
+  </si>
+  <si>
+    <t>защищенный ли</t>
+  </si>
+  <si>
+    <t>доступные категории предметов</t>
+  </si>
+  <si>
+    <t>вместимость</t>
+  </si>
+  <si>
+    <t>размер контейнера</t>
+  </si>
+  <si>
+    <t>модицикаций крайне много, все свойства перечислять -- смешно и крайне сложно. Проще будет их описывать в JSON или в чем-то этом духе. Работать с этим в SQL будет тяжело, проще указать ссылку на этот объект</t>
+  </si>
+  <si>
+    <t>тут надо строить ОГРОМНЫЙ граф, к этому моменту в БД должна быть заполнена всеми записями. Здесь мы будем хранить ID узла в этом графе</t>
+  </si>
+  <si>
+    <t>есть предметы, которые невозможно положить в спец.слот, потому что в рейде они ничего не делают, такие предметы ориентированы на использование в схроне (ремонтные наборы). В целом их классифицировать сложно, потому что они специфичны (маркеры, наборы для минирования, дальномер и т.д.)</t>
+  </si>
+  <si>
+    <t>ресурс использования. В целом этот столбец исключительно справочный, нужен только для удобного сравнения</t>
+  </si>
+  <si>
+    <t>true, если лечит. Можно было бы аптечки вынести в другую сущность, но у некоторых аптечек есть уникальные свойства, например, AFAK за 170 ед. останавливает сильное кровотечение, Grizzly за 50 ед. устраняет перелом, а также не все аптечки устраняют радицационное заражение и т.д.</t>
+  </si>
+  <si>
+    <t>null -- значит не устраняет, N -- тратит ресурс использования</t>
+  </si>
+  <si>
+    <t>null -- значит не устраняет, N -- тратит ресурс использования. Для гемостатиков это значение 1</t>
+  </si>
+  <si>
+    <t>null -- значит не устраняет, N -- тратит ресурс использования. Для бинтов это значение 1</t>
+  </si>
+  <si>
+    <t>измеряем в секундах</t>
+  </si>
+  <si>
+    <t>измеряется в секундах. Это прикол звездочки, она снимает контузию, но еще и накладывает ее (звездочка в целом не предмет, а сплошной прикол, она изначально была добавлена лечить переломы, а резерв, до кучи, можно и не упоминать)</t>
+  </si>
+  <si>
+    <t>занес защищенные кейсы в ту же категорию для простоты. true, если это альфа, каппа, эпсилон и т.д.</t>
+  </si>
+  <si>
+    <t>В игре не описано что можно класть в какие контейнеры. в целом, такого строгого учета предметов не надо, поэтому можно в свободной форме описать что можно положить в контейнер.</t>
+  </si>
+  <si>
+    <t>у некоторых контейнеров сложная структура вместимости, проще приложить скрин</t>
+  </si>
+  <si>
+    <t>для наглядности здесь будет число</t>
+  </si>
+  <si>
+    <t>таблица ключей</t>
+  </si>
+  <si>
+    <t>for_location</t>
+  </si>
+  <si>
+    <t>what_opening</t>
+  </si>
+  <si>
+    <t>where_found</t>
+  </si>
+  <si>
+    <t>what_inside</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>ID ключа</t>
+  </si>
+  <si>
+    <t>для локации</t>
+  </si>
+  <si>
+    <t>что открывает</t>
+  </si>
+  <si>
+    <t>где найти</t>
+  </si>
+  <si>
+    <t>что внутри</t>
+  </si>
+  <si>
+    <t>количество использований</t>
+  </si>
+  <si>
+    <t>если ключ мультикартовый, то в виде текста перечисляем ID карт. Если для одной карты, то храним одно ID, парсить будем</t>
+  </si>
+  <si>
+    <t>ссылка на гайд</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -597,6 +1266,21 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="6">
@@ -758,7 +1442,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -786,6 +1470,9 @@
     <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -801,6 +1488,7 @@
     <xf borderId="9" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="10" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -831,9 +1519,6 @@
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="10" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -846,6 +1531,9 @@
     <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -858,8 +1546,15 @@
     <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -867,13 +1562,78 @@
     <xf borderId="10" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="14" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="14" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1095,26 +1855,33 @@
     <col customWidth="1" min="2" max="2" width="32.5"/>
     <col customWidth="1" min="3" max="3" width="30.0"/>
     <col customWidth="1" min="4" max="4" width="19.38"/>
-    <col customWidth="1" min="5" max="6" width="20.13"/>
+    <col customWidth="1" min="5" max="5" width="36.25"/>
+    <col customWidth="1" min="6" max="6" width="34.63"/>
     <col customWidth="1" min="7" max="7" width="20.63"/>
     <col customWidth="1" min="8" max="8" width="31.5"/>
-    <col customWidth="1" min="9" max="9" width="20.25"/>
-    <col customWidth="1" min="10" max="10" width="27.63"/>
-    <col customWidth="1" min="11" max="11" width="19.13"/>
-    <col customWidth="1" min="12" max="12" width="24.25"/>
-    <col customWidth="1" min="13" max="13" width="21.88"/>
-    <col customWidth="1" min="14" max="14" width="19.75"/>
-    <col customWidth="1" min="15" max="15" width="25.25"/>
-    <col customWidth="1" min="16" max="16" width="20.13"/>
-    <col customWidth="1" min="17" max="17" width="21.88"/>
+    <col customWidth="1" min="9" max="9" width="22.88"/>
+    <col customWidth="1" min="10" max="10" width="62.88"/>
+    <col customWidth="1" min="11" max="11" width="34.5"/>
+    <col customWidth="1" min="12" max="12" width="33.63"/>
+    <col customWidth="1" min="13" max="13" width="33.25"/>
+    <col customWidth="1" min="14" max="14" width="39.75"/>
+    <col customWidth="1" min="15" max="15" width="33.5"/>
+    <col customWidth="1" min="16" max="16" width="43.75"/>
+    <col customWidth="1" min="17" max="17" width="33.75"/>
     <col customWidth="1" min="18" max="18" width="22.88"/>
     <col customWidth="1" min="19" max="19" width="18.63"/>
-    <col customWidth="1" min="20" max="20" width="31.88"/>
+    <col customWidth="1" min="20" max="20" width="26.25"/>
     <col customWidth="1" min="21" max="21" width="30.25"/>
-    <col customWidth="1" min="22" max="23" width="23.5"/>
-    <col customWidth="1" min="24" max="24" width="13.88"/>
-    <col customWidth="1" min="25" max="25" width="18.88"/>
-    <col customWidth="1" min="26" max="26" width="63.63"/>
+    <col customWidth="1" min="22" max="22" width="28.13"/>
+    <col customWidth="1" min="23" max="23" width="38.5"/>
+    <col customWidth="1" min="24" max="24" width="28.88"/>
+    <col customWidth="1" min="25" max="25" width="27.88"/>
+    <col customWidth="1" min="26" max="26" width="62.88"/>
+    <col customWidth="1" min="27" max="27" width="26.63"/>
+    <col customWidth="1" min="28" max="28" width="24.88"/>
+    <col customWidth="1" min="29" max="29" width="31.88"/>
+    <col customWidth="1" min="30" max="30" width="24.38"/>
+    <col customWidth="1" min="31" max="31" width="31.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,1022 +1918,2868 @@
         <v>7</v>
       </c>
       <c r="T1" s="4"/>
+      <c r="V1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="4"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>8</v>
-      </c>
       <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="S2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>21</v>
+      <c r="W2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA2" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="H3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="I3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="T3" s="15" t="s">
+      <c r="L3" s="13" t="s">
         <v>38</v>
       </c>
+      <c r="M3" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="S4" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="15" t="s">
-        <v>49</v>
-      </c>
+      <c r="A4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="S4" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="T4" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB4" s="17"/>
+      <c r="AC4" s="17"/>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="T5" s="20" t="s">
-        <v>55</v>
-      </c>
+      <c r="A5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="T5" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y5" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
     </row>
     <row r="6">
-      <c r="A6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="A6" s="23"/>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>57</v>
+      <c r="A7" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
-      <c r="F7" s="24" t="s">
-        <v>58</v>
+      <c r="F7" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="4"/>
-      <c r="M7" s="25" t="s">
-        <v>60</v>
+      <c r="M7" s="27" t="s">
+        <v>77</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="4"/>
       <c r="T7" s="7" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="U7" s="8" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="4"/>
       <c r="Y7" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z7" s="26" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="Z7" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z8" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="V10" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z10" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q11" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="R11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="V8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y8" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="T9" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z9" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q10" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="R10" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="T10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="V10" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="W10" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Z10" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="O11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="R11" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="U11" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="V11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z11" s="16" t="s">
-        <v>51</v>
+      <c r="T11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V11" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="W11" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z11" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="O12" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="V12" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z12" s="30" t="s">
-        <v>116</v>
-      </c>
+      <c r="C12" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="O12" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="V12" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z12" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="32"/>
+      <c r="AD12" s="32"/>
+      <c r="AE12" s="32"/>
     </row>
     <row r="13">
-      <c r="C13" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="O13" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="V13" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z13" s="32" t="s">
-        <v>121</v>
-      </c>
+      <c r="C13" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="O13" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="V13" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="32"/>
     </row>
     <row r="14">
-      <c r="C14" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="O14" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="V14" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z14" s="33" t="s">
-        <v>120</v>
-      </c>
+      <c r="C14" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="O14" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="V14" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z14" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="32"/>
     </row>
     <row r="15">
-      <c r="C15" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="O15" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="V15" s="33" t="s">
-        <v>129</v>
-      </c>
+      <c r="C15" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="O15" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
     </row>
     <row r="16">
-      <c r="C16" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="O16" s="32" t="s">
-        <v>132</v>
-      </c>
+      <c r="C16" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="J16" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="O16" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
     </row>
     <row r="17">
-      <c r="C17" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="O17" s="32" t="s">
-        <v>135</v>
-      </c>
+      <c r="C17" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="O17" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
     </row>
     <row r="18">
-      <c r="C18" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="J18" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="O18" s="32" t="s">
-        <v>138</v>
-      </c>
+      <c r="C18" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="O18" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
     </row>
     <row r="19">
-      <c r="C19" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="O19" s="32" t="s">
-        <v>139</v>
-      </c>
+      <c r="C19" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="O19" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
     </row>
     <row r="20">
-      <c r="C20" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="O20" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="R20" s="21" t="s">
-        <v>142</v>
-      </c>
+      <c r="C20" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="O20" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
     </row>
     <row r="21">
-      <c r="C21" s="34" t="s">
-        <v>143</v>
-      </c>
+      <c r="C21" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
     </row>
     <row r="22">
-      <c r="C22" s="35"/>
+      <c r="C22" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="E23" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="4"/>
-      <c r="K23" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="Q23" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="4"/>
+      <c r="AB23" s="37"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>153</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="E24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>154</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="4"/>
       <c r="N24" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>154</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="4"/>
       <c r="T24" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>156</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="4"/>
+      <c r="AA24" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB24" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="4"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q25" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="R25" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="T25" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>166</v>
+      <c r="A25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="T25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="V25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W25" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="X25" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC25" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD25" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE25" s="7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" s="12" t="s">
+      <c r="A26" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="L26" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="O26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="P26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="T26" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="U26" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="V26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W26" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="X26" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Y26" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA26" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB26" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC26" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD26" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE26" s="40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="R27" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="T27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="V27" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="W27" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="X27" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA27" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB27" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC27" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD27" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE27" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="N28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="T28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="U28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="W28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="X28" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA28" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE28" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43"/>
+      <c r="H29" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="Q29" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="W29" s="31" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q30" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="W30" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q31" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="W31" s="34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q32" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="W32" s="35" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="U33" s="46"/>
+      <c r="AA33" s="17"/>
+      <c r="AB33" s="17"/>
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+    </row>
+    <row r="34">
+      <c r="H34" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA34" s="17"/>
+      <c r="AB34" s="17"/>
+      <c r="AC34" s="17"/>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
+    </row>
+    <row r="35">
+      <c r="H35" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17"/>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+    </row>
+    <row r="36">
+      <c r="H36" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA36" s="17"/>
+      <c r="AB36" s="17"/>
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+    </row>
+    <row r="37">
+      <c r="H37" s="45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="48"/>
+      <c r="T39" s="48"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="48"/>
+      <c r="W39" s="48"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+    </row>
+    <row r="40">
+      <c r="H40" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="I40" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="I44" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="I45" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="I46" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="43" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="50" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="4"/>
+      <c r="S49" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="T49" s="52" t="s">
+        <v>241</v>
+      </c>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="4"/>
+      <c r="Y49" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z49" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3"/>
+      <c r="AC49" s="4"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="H26" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q26" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="R26" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="S26" s="12" t="s">
+      <c r="C50" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="L50" s="23"/>
+      <c r="M50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="P50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q50" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="T26" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="O27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q27" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="R27" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="S27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="T27" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="U27" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="38"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="U28" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="U29" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="38"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="32" t="s">
+      <c r="S50" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="T50" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="U50" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="V50" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="W50" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z50" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA50" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AC50" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B51" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="L51" s="23"/>
+      <c r="M51" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="N51" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O51" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="P51" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q51" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="S51" s="56" t="s">
+        <v>188</v>
+      </c>
+      <c r="T51" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="U51" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="V51" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="W51" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y51" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z51" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="AA51" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB51" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="AC51" s="40" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B52" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="L52" s="23"/>
+      <c r="M52" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="O52" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="P52" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q52" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="S52" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="T52" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="U52" s="57" t="s">
+        <v>276</v>
+      </c>
+      <c r="V52" s="56" t="s">
+        <v>279</v>
+      </c>
+      <c r="W52" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y52" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z52" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA52" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB52" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC52" s="13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="L53" s="23"/>
+      <c r="M53" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="N53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="O53" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="S53" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="T53" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="U53" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="V53" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="W53" s="59" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y53" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z53" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB53" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC53" s="18" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43"/>
+      <c r="B54" s="61"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="43"/>
+      <c r="L54" s="62"/>
+      <c r="M54" s="43"/>
+      <c r="N54" s="43"/>
+      <c r="O54" s="61"/>
+      <c r="P54" s="43"/>
+      <c r="Q54" s="43"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="48"/>
+      <c r="T54" s="48"/>
+      <c r="U54" s="49"/>
+      <c r="V54" s="48"/>
+      <c r="W54" s="48"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="43"/>
+      <c r="Z54" s="43"/>
+      <c r="AA54" s="43"/>
+      <c r="AB54" s="43"/>
+      <c r="AC54" s="43"/>
+      <c r="AD54" s="17"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="43"/>
+      <c r="O55" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="P55" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="43"/>
+      <c r="AA55" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB55" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="4"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="N56" s="43"/>
+      <c r="O56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P56" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q56" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="R56" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="S56" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="T56" s="51" t="s">
+        <v>287</v>
+      </c>
+      <c r="U56" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="V56" s="51" t="s">
+        <v>300</v>
+      </c>
+      <c r="W56" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="X56" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y56" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="Z56" s="43"/>
+      <c r="AA56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB56" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC56" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="AD56" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE56" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="B57" s="63" t="s">
+        <v>307</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>308</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>309</v>
+      </c>
+      <c r="E57" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="F57" s="40" t="s">
+        <v>311</v>
+      </c>
+      <c r="G57" s="40" t="s">
+        <v>312</v>
+      </c>
+      <c r="H57" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="I57" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="J57" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="K57" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="L57" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="N57" s="43"/>
+      <c r="O57" s="40" t="s">
+        <v>319</v>
+      </c>
+      <c r="P57" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q57" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="R57" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="S57" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="T57" s="58" t="s">
+        <v>309</v>
+      </c>
+      <c r="U57" s="58" t="s">
+        <v>323</v>
+      </c>
+      <c r="V57" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="W57" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="X57" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y57" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="Z57" s="43"/>
+      <c r="AA57" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB57" s="40" t="s">
+        <v>328</v>
+      </c>
+      <c r="AC57" s="40" t="s">
+        <v>329</v>
+      </c>
+      <c r="AD57" s="40" t="s">
+        <v>330</v>
+      </c>
+      <c r="AE57" s="40" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B58" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="M58" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="N58" s="43"/>
+      <c r="O58" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="P58" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="R58" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="S58" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="T58" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="U58" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="V58" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="W58" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="X58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z58" s="43"/>
+      <c r="AA58" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD58" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE58" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="M59" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="N59" s="43"/>
+      <c r="O59" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="P59" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R59" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="S59" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="T59" s="64" t="s">
         <v>128</v>
       </c>
-      <c r="U30" s="32" t="s">
+      <c r="U59" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="V59" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="W59" s="64" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="38"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="U31" s="33" t="s">
-        <v>132</v>
-      </c>
+      <c r="X59" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y59" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z59" s="43"/>
+      <c r="AA59" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD59" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE59" s="18" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43"/>
+      <c r="B60" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="C60" s="43" t="s">
+        <v>340</v>
+      </c>
+      <c r="D60" s="17"/>
+      <c r="E60" s="43"/>
+      <c r="F60" s="43"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="43"/>
+      <c r="J60" s="43"/>
+      <c r="K60" s="43"/>
+      <c r="L60" s="62"/>
+      <c r="M60" s="43"/>
+      <c r="N60" s="43"/>
+      <c r="O60" s="61"/>
+      <c r="P60" s="43"/>
+      <c r="Q60" s="43"/>
+      <c r="R60" s="17"/>
+      <c r="S60" s="48"/>
+      <c r="T60" s="48"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="48"/>
+      <c r="W60" s="48"/>
+      <c r="X60" s="17"/>
+      <c r="Y60" s="43"/>
+      <c r="Z60" s="43"/>
+      <c r="AA60" s="43"/>
+      <c r="AB60" s="43"/>
+      <c r="AC60" s="43"/>
+      <c r="AD60" s="17"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B61" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" s="65" t="s">
+        <v>342</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="48"/>
+      <c r="W61" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="X61" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="43"/>
+      <c r="AC61" s="43"/>
+      <c r="AD61" s="17"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="53" t="s">
+        <v>345</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D62" s="17"/>
+      <c r="E62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="M62" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="O62" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="P62" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q62" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="R62" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="S62" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="T62" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="U62" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="V62" s="48"/>
+      <c r="W62" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="X62" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y62" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="Z62" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="AA62" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="AB62" s="43"/>
+      <c r="AC62" s="43"/>
+      <c r="AD62" s="17"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="B63" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I63" s="40" t="s">
+        <v>328</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="L63" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="M63" s="58" t="s">
+        <v>366</v>
+      </c>
+      <c r="N63" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="O63" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="P63" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q63" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="R63" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="S63" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="T63" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="U63" s="58" t="s">
+        <v>318</v>
+      </c>
+      <c r="V63" s="48"/>
+      <c r="W63" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="X63" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y63" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z63" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA63" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB63" s="43"/>
+      <c r="AC63" s="43"/>
+      <c r="AD63" s="17"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B64" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="D64" s="17"/>
+      <c r="E64" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="I64" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="L64" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="M64" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="N64" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="O64" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="P64" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q64" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="R64" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="S64" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="T64" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U64" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="V64" s="48"/>
+      <c r="W64" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="X64" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="Y64" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="Z64" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="AA64" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="AB64" s="43"/>
+      <c r="AC64" s="43"/>
+      <c r="AD64" s="17"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" s="17"/>
+      <c r="E65" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J65" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K65" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="M65" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="N65" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="O65" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="P65" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q65" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="R65" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="S65" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="T65" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="U65" s="64" t="s">
+        <v>213</v>
+      </c>
+      <c r="V65" s="48"/>
+      <c r="W65" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="X65" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y65" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z65" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA65" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB65" s="43"/>
+      <c r="AC65" s="43"/>
+      <c r="AD65" s="17"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="43"/>
+      <c r="B66" s="61"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="43"/>
+      <c r="L66" s="43"/>
+      <c r="M66" s="66"/>
+      <c r="N66" s="43"/>
+      <c r="O66" s="61"/>
+      <c r="P66" s="43"/>
+      <c r="Q66" s="43"/>
+      <c r="R66" s="43"/>
+      <c r="S66" s="66"/>
+      <c r="T66" s="43"/>
+      <c r="U66" s="66"/>
+      <c r="V66" s="48"/>
+      <c r="W66" s="66"/>
+      <c r="X66" s="43"/>
+      <c r="Y66" s="43"/>
+      <c r="Z66" s="43"/>
+      <c r="AA66" s="43"/>
+      <c r="AB66" s="43"/>
+      <c r="AC66" s="43"/>
+      <c r="AD66" s="17"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="4"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="43"/>
+      <c r="J67" s="43"/>
+      <c r="K67" s="43"/>
+      <c r="L67" s="43"/>
+      <c r="M67" s="66"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="61"/>
+      <c r="P67" s="43"/>
+      <c r="Q67" s="43"/>
+      <c r="R67" s="43"/>
+      <c r="S67" s="66"/>
+      <c r="T67" s="43"/>
+      <c r="U67" s="66"/>
+      <c r="V67" s="48"/>
+      <c r="W67" s="66"/>
+      <c r="X67" s="43"/>
+      <c r="Y67" s="43"/>
+      <c r="Z67" s="43"/>
+      <c r="AA67" s="43"/>
+      <c r="AB67" s="43"/>
+      <c r="AC67" s="43"/>
+      <c r="AD67" s="17"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
+      <c r="J68" s="43"/>
+      <c r="K68" s="43"/>
+      <c r="L68" s="43"/>
+      <c r="M68" s="66"/>
+      <c r="N68" s="43"/>
+      <c r="O68" s="61"/>
+      <c r="P68" s="43"/>
+      <c r="Q68" s="43"/>
+      <c r="R68" s="43"/>
+      <c r="S68" s="66"/>
+      <c r="T68" s="43"/>
+      <c r="U68" s="66"/>
+      <c r="V68" s="48"/>
+      <c r="W68" s="66"/>
+      <c r="X68" s="43"/>
+      <c r="Y68" s="43"/>
+      <c r="Z68" s="43"/>
+      <c r="AA68" s="43"/>
+      <c r="AB68" s="43"/>
+      <c r="AC68" s="43"/>
+      <c r="AD68" s="17"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+      <c r="L69" s="43"/>
+      <c r="M69" s="66"/>
+      <c r="N69" s="43"/>
+      <c r="O69" s="61"/>
+      <c r="P69" s="43"/>
+      <c r="Q69" s="43"/>
+      <c r="R69" s="43"/>
+      <c r="S69" s="66"/>
+      <c r="T69" s="43"/>
+      <c r="U69" s="66"/>
+      <c r="V69" s="48"/>
+      <c r="W69" s="66"/>
+      <c r="X69" s="43"/>
+      <c r="Y69" s="43"/>
+      <c r="Z69" s="43"/>
+      <c r="AA69" s="43"/>
+      <c r="AB69" s="43"/>
+      <c r="AC69" s="43"/>
+      <c r="AD69" s="17"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H70" s="43"/>
+      <c r="I70" s="43"/>
+      <c r="J70" s="43"/>
+      <c r="K70" s="43"/>
+      <c r="L70" s="43"/>
+      <c r="M70" s="66"/>
+      <c r="N70" s="43"/>
+      <c r="O70" s="61"/>
+      <c r="P70" s="43"/>
+      <c r="Q70" s="43"/>
+      <c r="R70" s="43"/>
+      <c r="S70" s="66"/>
+      <c r="T70" s="43"/>
+      <c r="U70" s="66"/>
+      <c r="V70" s="48"/>
+      <c r="W70" s="66"/>
+      <c r="X70" s="43"/>
+      <c r="Y70" s="43"/>
+      <c r="Z70" s="43"/>
+      <c r="AA70" s="43"/>
+      <c r="AB70" s="43"/>
+      <c r="AC70" s="43"/>
+      <c r="AD70" s="17"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="E71" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H71" s="43"/>
+      <c r="I71" s="43"/>
+      <c r="J71" s="43"/>
+      <c r="K71" s="43"/>
+      <c r="L71" s="43"/>
+      <c r="M71" s="66"/>
+      <c r="N71" s="43"/>
+      <c r="O71" s="61"/>
+      <c r="P71" s="43"/>
+      <c r="Q71" s="43"/>
+      <c r="R71" s="43"/>
+      <c r="S71" s="66"/>
+      <c r="T71" s="43"/>
+      <c r="U71" s="66"/>
+      <c r="V71" s="48"/>
+      <c r="W71" s="66"/>
+      <c r="X71" s="43"/>
+      <c r="Y71" s="43"/>
+      <c r="Z71" s="43"/>
+      <c r="AA71" s="43"/>
+      <c r="AB71" s="43"/>
+      <c r="AC71" s="43"/>
+      <c r="AD71" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="52">
+    <mergeCell ref="F49:K49"/>
+    <mergeCell ref="N49:Q49"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="M24:M28"/>
+    <mergeCell ref="S24:S28"/>
+    <mergeCell ref="A29:G48"/>
+    <mergeCell ref="J29:P48"/>
+    <mergeCell ref="I29:I37"/>
+    <mergeCell ref="U1:U5"/>
+    <mergeCell ref="X1:X5"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:G5"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:K5"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:Q5"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="X7:X11"/>
+    <mergeCell ref="Z15:Z28"/>
+    <mergeCell ref="V16:V23"/>
+    <mergeCell ref="U24:Y24"/>
+    <mergeCell ref="A6:AA6"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="R23:U23"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="E7:E11"/>
     <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:L11"/>
     <mergeCell ref="N7:R7"/>
-    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="S7:S11"/>
+    <mergeCell ref="F24:L24"/>
+    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="AB24:AE24"/>
+    <mergeCell ref="A12:B23"/>
+    <mergeCell ref="D12:I23"/>
+    <mergeCell ref="K12:N23"/>
+    <mergeCell ref="P12:U23"/>
+    <mergeCell ref="W12:Y23"/>
+    <mergeCell ref="J19:J23"/>
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="I61:U61"/>
+    <mergeCell ref="X61:AA61"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:D53"/>
+    <mergeCell ref="T49:W49"/>
+    <mergeCell ref="Z49:AC49"/>
+    <mergeCell ref="B55:M55"/>
+    <mergeCell ref="P55:Y55"/>
+    <mergeCell ref="AB55:AE55"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
